--- a/docs/テスト結果.xlsx
+++ b/docs/テスト結果.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="180">
   <si>
     <t>テスト結果エビデンス</t>
   </si>
@@ -26,421 +26,430 @@
     <t>実施日</t>
   </si>
   <si>
+    <t>2026-08-26（PostgreSQL移行後の再実施。旧実施日2026-08-25はH2環境時点）</t>
+  </si>
+  <si>
+    <t>実施者</t>
+  </si>
+  <si>
+    <t>Claude Code</t>
+  </si>
+  <si>
+    <t>実施件数</t>
+  </si>
+  <si>
+    <t>48 件</t>
+  </si>
+  <si>
+    <t>OK（成功）</t>
+  </si>
+  <si>
+    <t>NG（不具合あり）</t>
+  </si>
+  <si>
+    <t>0 件</t>
+  </si>
+  <si>
+    <t>■ 前回(H2環境/2026-08-25)でNGだった項目の再テスト結果（今回はすべてOK）</t>
+  </si>
+  <si>
+    <t>テストID</t>
+  </si>
+  <si>
+    <t>シート</t>
+  </si>
+  <si>
+    <t>テスト項目</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>ITEM-005</t>
+  </si>
+  <si>
+    <t>商品管理機能</t>
+  </si>
+  <si>
+    <t>商品コード重複登録（画面）</t>
+  </si>
+  <si>
+    <t>バグ修正.xlsxのとおり2026-08-25にDuplicateBarcodeExceptionを新設し修正済み。2026-08-26にPostgreSQL環境で再実施し、重複登録時に「この商品コードは既に使用されています」等の適切なエラーメッセージが表示され、DBにも重複行が作られないことを確認（OK）</t>
+  </si>
+  <si>
+    <t>ITEM-007</t>
+  </si>
+  <si>
+    <t>必須項目未入力（サーバー直送）</t>
+  </si>
+  <si>
+    <t>バグ修正.xlsxのとおり2026-08-25にItemPageControllerへ@Validを追加し修正済み。2026-08-26にPostgreSQL環境で再実施し、200で「商品名を入力してください」等のエラーメッセージが表示されることを確認（OK）</t>
+  </si>
+  <si>
+    <t>POS-005</t>
+  </si>
+  <si>
+    <t>レジ機能(POS)</t>
+  </si>
+  <si>
+    <t>空欄でクイック追加</t>
+  </si>
+  <si>
+    <t>バグ修正.xlsxのとおり2026-08-25にpos.htmlの「カートに追加」ボタンへformnovalidateを追加し修正済み。2026-08-26にPostgreSQL環境で再実施し、空欄でも案内メッセージが表示されることを確認（OK）</t>
+  </si>
+  <si>
+    <t>商品管理機能 テスト結果エビデンス</t>
+  </si>
+  <si>
+    <t>全14件</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>結果</t>
+  </si>
+  <si>
+    <t>確認内容</t>
+  </si>
+  <si>
+    <t>スクリーンショット</t>
+  </si>
+  <si>
+    <t>ITEM-001</t>
+  </si>
+  <si>
+    <t>商品一覧表示</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>商品一覧に初期データ6件を含む商品が表示されることを確認（2026-08-26、実ブラウザ(Playwright)で再撮影）</t>
+  </si>
+  <si>
+    <t>ITEM-002</t>
+  </si>
+  <si>
+    <t>商品新規登録（画面）</t>
+  </si>
+  <si>
+    <t>一覧に新規商品C010(リップグロス)が追加されたことを確認</t>
+  </si>
+  <si>
+    <t>ITEM-003</t>
+  </si>
+  <si>
+    <t>商品編集（画面）</t>
+  </si>
+  <si>
+    <t>C010の価格が2000円に更新されたことを確認</t>
+  </si>
+  <si>
+    <t>ITEM-004</t>
+  </si>
+  <si>
+    <t>商品削除（画面）</t>
+  </si>
+  <si>
+    <t>C010が一覧から削除されたことを確認</t>
+  </si>
+  <si>
+    <t>修正済み（2026-08-25）。PostgreSQL環境で再実施：barcode=C001で登録しようとすると「この商品コードは既に使用されています: C001」が表示され登録フォームに留まる。DB(item)に重複行が作られないことをpsqlで確認（2026-08-26、実ブラウザ(Playwright)で再撮影して確認）</t>
+  </si>
+  <si>
+    <t>ITEM-006</t>
+  </si>
+  <si>
+    <t>必須項目未入力（ブラウザ経由）</t>
+  </si>
+  <si>
+    <t>ブラウザのHTML5必須チェックにより送信がブロックされ、ページ遷移しなかったことを確認</t>
+  </si>
+  <si>
+    <t>修正済み（2026-08-25）。PostgreSQL環境で再実施：/items へname省略でPOSTすると200で「商品名を入力してください」が表示され、INSERTされないことをpsqlで確認（barcode=C097が0件）</t>
+  </si>
+  <si>
+    <t>ITEM-008</t>
+  </si>
+  <si>
+    <t>価格・在庫に0を指定</t>
+  </si>
+  <si>
+    <t>price=0, stock=0 で登録できることを確認</t>
+  </si>
+  <si>
+    <t>ITEM-009</t>
+  </si>
+  <si>
+    <t>価格に負数を指定（REST API）</t>
+  </si>
+  <si>
+    <t>@Valid によるバリデーションで400 Bad Requestが返ることを確認</t>
+  </si>
+  <si>
+    <t>ITEM-010</t>
+  </si>
+  <si>
+    <t>REST API：一覧取得</t>
+  </si>
+  <si>
+    <t>200 OK、barcodeを含む7件のJSON配列が返ることを確認</t>
+  </si>
+  <si>
+    <t>ITEM-011</t>
+  </si>
+  <si>
+    <t>REST API：新規登録</t>
+  </si>
+  <si>
+    <t>201 Created、登録内容(id=10)がJSONで返ることを確認</t>
+  </si>
+  <si>
+    <t>ITEM-012</t>
+  </si>
+  <si>
+    <t>REST API：更新</t>
+  </si>
+  <si>
+    <t>200 OK、更新後の内容が返ることを確認</t>
+  </si>
+  <si>
+    <t>ITEM-013</t>
+  </si>
+  <si>
+    <t>REST API：削除</t>
+  </si>
+  <si>
+    <t>204 No Contentが返ることを確認</t>
+  </si>
+  <si>
+    <t>ITEM-014</t>
+  </si>
+  <si>
+    <t>存在しないIDの取得／更新／削除</t>
+  </si>
+  <si>
+    <t>GET/PUT/DELETEいずれも404 Not Foundが返ることを確認</t>
+  </si>
+  <si>
+    <t>レジ機能(POS) テスト結果エビデンス</t>
+  </si>
+  <si>
+    <t>全22件</t>
+  </si>
+  <si>
+    <t>POS-001</t>
+  </si>
+  <si>
+    <t>クイック追加（商品コード）</t>
+  </si>
+  <si>
+    <t>C001をクイック追加し、カート合計が1200円になることを確認</t>
+  </si>
+  <si>
+    <t>POS-002</t>
+  </si>
+  <si>
+    <t>クイック追加の数量累積</t>
+  </si>
+  <si>
+    <t>新しい行が増えず、数量が2件ぶんに加算され合計2400円になることを確認</t>
+  </si>
+  <si>
+    <t>POS-003</t>
+  </si>
+  <si>
+    <t>商品名でのクイック追加</t>
+  </si>
+  <si>
+    <t>商品名の部分一致でカートに追加されることを確認</t>
+  </si>
+  <si>
+    <t>POS-004</t>
+  </si>
+  <si>
+    <t>存在しないコードでクイック追加</t>
+  </si>
+  <si>
+    <t>エラーメッセージが表示され、カート内容は変化しないことを確認</t>
+  </si>
+  <si>
+    <t>修正済み（2026-08-25、pos.htmlの「カートに追加」ボタンへformnovalidate追加）。PostgreSQL環境で再実施：keyword="" で送信すると「商品コードまたは商品名を入力してください」が表示されることを確認（2026-08-26、実ブラウザ(Playwright)で再撮影して確認）</t>
+  </si>
+  <si>
+    <t>POS-006</t>
+  </si>
+  <si>
+    <t>検索（空欄）→全件ポップアップ表示</t>
+  </si>
+  <si>
+    <t>空欄検索でポップアップに登録済み全7件が表示されることを確認</t>
+  </si>
+  <si>
+    <t>POS-007</t>
+  </si>
+  <si>
+    <t>検索（キーワード）→絞り込み表示</t>
+  </si>
+  <si>
+    <t>キーワード検索でポップアップに該当商品のみ表示されることを確認</t>
+  </si>
+  <si>
+    <t>POS-008</t>
+  </si>
+  <si>
+    <t>ポップアップ内検索ボックスでの再検索</t>
+  </si>
+  <si>
+    <t>ポップアップを閉じずに再検索の結果が更新されることを確認</t>
+  </si>
+  <si>
+    <t>POS-009</t>
+  </si>
+  <si>
+    <t>検索結果からカートに追加</t>
+  </si>
+  <si>
+    <t>ポップアップが閉じ、選択した商品がカートに反映されることを確認</t>
+  </si>
+  <si>
+    <t>POS-010</t>
+  </si>
+  <si>
+    <t>検索結果0件</t>
+  </si>
+  <si>
+    <t>ポップアップ内に該当なしのメッセージが表示されることを確認</t>
+  </si>
+  <si>
+    <t>POS-011</t>
+  </si>
+  <si>
+    <t>カートから商品削除</t>
+  </si>
+  <si>
+    <t>該当行がカートから削除され、合計金額が再計算されることを確認</t>
+  </si>
+  <si>
+    <t>POS-012</t>
+  </si>
+  <si>
+    <t>カートを空にする</t>
+  </si>
+  <si>
+    <t>カートが空になることを確認</t>
+  </si>
+  <si>
+    <t>POS-013</t>
+  </si>
+  <si>
+    <t>カートが空の状態での画面表示</t>
+  </si>
+  <si>
+    <t>カートが空の間は「会計へ進む」ボタンが表示されないことを確認</t>
+  </si>
+  <si>
+    <t>POS-014</t>
+  </si>
+  <si>
+    <t>会計へ進む</t>
+  </si>
+  <si>
+    <t>/pos/payment に遷移し合計金額が表示されることを確認</t>
+  </si>
+  <si>
+    <t>POS-015</t>
+  </si>
+  <si>
+    <t>お釣りのリアルタイム計算</t>
+  </si>
+  <si>
+    <t>2026-08-26、実ブラウザ(Playwright)で確認：お預かり金額2000円入力時、ページ遷移せずJavaScriptで即座に「お釣り: 800円」が表示されることをスクリーンショットで確認</t>
+  </si>
+  <si>
+    <t>POS-016</t>
+  </si>
+  <si>
+    <t>お預かり金額が合計未満</t>
+  </si>
+  <si>
+    <t>エラーメッセージが表示され支払い画面に留まることを確認</t>
+  </si>
+  <si>
+    <t>POS-017</t>
+  </si>
+  <si>
+    <t>会計確定（単一商品）</t>
+  </si>
+  <si>
+    <t>領収画面に遷移し合計1200円・お預かり2000円・お釣り800円が表示されることを確認（2026-08-26、実ブラウザ(Playwright)で再撮影）</t>
+  </si>
+  <si>
+    <t>POS-018</t>
+  </si>
+  <si>
+    <t>会計確定（複数商品・複数点）</t>
+  </si>
+  <si>
+    <t>2商品(化粧水x2, 口紅x1)、合計4200円で領収画面に明細が表示されることを確認</t>
+  </si>
+  <si>
+    <t>POS-019</t>
+  </si>
+  <si>
+    <t>在庫不足での会計確定（単一商品）</t>
+  </si>
+  <si>
+    <t>在庫(10)を超える数量(11)での会計時にエラーが表示され、支払い画面に留まることを確認</t>
+  </si>
+  <si>
+    <t>POS-020</t>
+  </si>
+  <si>
+    <t>複数商品中1点だけ在庫不足（ロールバック確認）</t>
+  </si>
+  <si>
+    <t>エラーが表示され、在庫十分だった商品(C004:15)も減算されていないことを確認（トランザクションロールバック）</t>
+  </si>
+  <si>
+    <t>POS-022</t>
+  </si>
+  <si>
+    <t>お預かり金額＝合計金額ちょうど</t>
+  </si>
+  <si>
+    <t>お預かり金額が合計と同額(3500円)の場合、お釣り0円で成立することを確認</t>
+  </si>
+  <si>
+    <t>POS-021</t>
+  </si>
+  <si>
+    <t>会計後のカートクリア</t>
+  </si>
+  <si>
+    <t>会計確定後、カートが空の状態で/posに戻ることを確認</t>
+  </si>
+  <si>
+    <t>売上履歴機能 テスト結果エビデンス</t>
+  </si>
+  <si>
+    <t>全3件</t>
+  </si>
+  <si>
+    <t>SALES-002</t>
+  </si>
+  <si>
+    <t>売上0件時の表示</t>
+  </si>
+  <si>
     <t>2026-08-25</t>
   </si>
   <si>
-    <t>実施者</t>
-  </si>
-  <si>
-    <t>Claude Code</t>
-  </si>
-  <si>
-    <t>実施件数</t>
-  </si>
-  <si>
-    <t>48 件</t>
-  </si>
-  <si>
-    <t>OK（成功）</t>
-  </si>
-  <si>
-    <t>45 件</t>
-  </si>
-  <si>
-    <t>NG（不具合あり）</t>
-  </si>
-  <si>
-    <t>3 件</t>
-  </si>
-  <si>
-    <t>■ NG（不具合）一覧</t>
-  </si>
-  <si>
-    <t>テストID</t>
-  </si>
-  <si>
-    <t>シート</t>
-  </si>
-  <si>
-    <t>テスト項目</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>ITEM-005</t>
-  </si>
-  <si>
-    <t>商品管理機能</t>
-  </si>
-  <si>
-    <t>商品コード重複登録（画面）</t>
-  </si>
-  <si>
-    <t>仕様どおり例外未処理のため500エラー画面となった（既知の未対応事項。プログラム改修は未実施）</t>
-  </si>
-  <si>
-    <t>ITEM-007</t>
-  </si>
-  <si>
-    <t>必須項目未入力（サーバー直送）</t>
-  </si>
-  <si>
-    <t>サーバー側の入力チェックが無く、Bean Validation例外で 500 エラーとなった（既知の未対応事項。プログラム改修は未実施）</t>
-  </si>
-  <si>
-    <t>POS-005</t>
-  </si>
-  <si>
-    <t>レジ機能(POS)</t>
-  </si>
-  <si>
-    <t>空欄でクイック追加</t>
-  </si>
-  <si>
-    <t>テキストボックスに required 属性があり、かつ「カートに追加」ボタンに formnovalidate が無いため、空欄のまま押してもブラウザのHTML5必須チェックでブロックされ、サーバーへ送信されない。そのため仕様書記載の案内メッセージ「商品コードまたは商品名を入力してください」は実際の画面操作では表示されない（直前のPOS-004の結果が画面に残ったままとなる）。プログラム改修は未実施。</t>
-  </si>
-  <si>
-    <t>商品管理機能 テスト結果エビデンス</t>
-  </si>
-  <si>
-    <t>全14件</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>結果</t>
-  </si>
-  <si>
-    <t>確認内容</t>
-  </si>
-  <si>
-    <t>スクリーンショット</t>
-  </si>
-  <si>
-    <t>ITEM-001</t>
-  </si>
-  <si>
-    <t>商品一覧表示</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>商品一覧に初期データ6件を含む商品が表示されることを確認</t>
-  </si>
-  <si>
-    <t>ITEM-002</t>
-  </si>
-  <si>
-    <t>商品新規登録（画面）</t>
-  </si>
-  <si>
-    <t>一覧に新規商品C010(リップグロス)が追加されたことを確認</t>
-  </si>
-  <si>
-    <t>ITEM-003</t>
-  </si>
-  <si>
-    <t>商品編集（画面）</t>
-  </si>
-  <si>
-    <t>C010の価格が2000円に更新されたことを確認</t>
-  </si>
-  <si>
-    <t>ITEM-004</t>
-  </si>
-  <si>
-    <t>商品削除（画面）</t>
-  </si>
-  <si>
-    <t>C010が一覧から削除されたことを確認</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>ITEM-006</t>
-  </si>
-  <si>
-    <t>必須項目未入力（ブラウザ経由）</t>
-  </si>
-  <si>
-    <t>ブラウザのHTML5必須チェックにより送信がブロックされ、ページ遷移しなかったことを確認</t>
-  </si>
-  <si>
-    <t>ITEM-008</t>
-  </si>
-  <si>
-    <t>価格・在庫に0を指定</t>
-  </si>
-  <si>
-    <t>price=0, stock=0 で登録できることを確認</t>
-  </si>
-  <si>
-    <t>ITEM-009</t>
-  </si>
-  <si>
-    <t>価格に負数を指定（REST API）</t>
-  </si>
-  <si>
-    <t>@Valid によるバリデーションで400 Bad Requestが返ることを確認</t>
-  </si>
-  <si>
-    <t>ITEM-010</t>
-  </si>
-  <si>
-    <t>REST API：一覧取得</t>
-  </si>
-  <si>
-    <t>200 OK、barcodeを含む7件のJSON配列が返ることを確認</t>
-  </si>
-  <si>
-    <t>ITEM-011</t>
-  </si>
-  <si>
-    <t>REST API：新規登録</t>
-  </si>
-  <si>
-    <t>201 Created、登録内容(id=10)がJSONで返ることを確認</t>
-  </si>
-  <si>
-    <t>ITEM-012</t>
-  </si>
-  <si>
-    <t>REST API：更新</t>
-  </si>
-  <si>
-    <t>200 OK、更新後の内容が返ることを確認</t>
-  </si>
-  <si>
-    <t>ITEM-013</t>
-  </si>
-  <si>
-    <t>REST API：削除</t>
-  </si>
-  <si>
-    <t>204 No Contentが返ることを確認</t>
-  </si>
-  <si>
-    <t>ITEM-014</t>
-  </si>
-  <si>
-    <t>存在しないIDの取得／更新／削除</t>
-  </si>
-  <si>
-    <t>GET/PUT/DELETEいずれも404 Not Foundが返ることを確認</t>
-  </si>
-  <si>
-    <t>レジ機能(POS) テスト結果エビデンス</t>
-  </si>
-  <si>
-    <t>全22件</t>
-  </si>
-  <si>
-    <t>POS-001</t>
-  </si>
-  <si>
-    <t>クイック追加（商品コード）</t>
-  </si>
-  <si>
-    <t>C001をクイック追加し、カート合計が1200円になることを確認</t>
-  </si>
-  <si>
-    <t>POS-002</t>
-  </si>
-  <si>
-    <t>クイック追加の数量累積</t>
-  </si>
-  <si>
-    <t>新しい行が増えず、数量が2件ぶんに加算され合計2400円になることを確認</t>
-  </si>
-  <si>
-    <t>POS-003</t>
-  </si>
-  <si>
-    <t>商品名でのクイック追加</t>
-  </si>
-  <si>
-    <t>商品名の部分一致でカートに追加されることを確認</t>
-  </si>
-  <si>
-    <t>POS-004</t>
-  </si>
-  <si>
-    <t>存在しないコードでクイック追加</t>
-  </si>
-  <si>
-    <t>エラーメッセージが表示され、カート内容は変化しないことを確認</t>
-  </si>
-  <si>
-    <t>POS-006</t>
-  </si>
-  <si>
-    <t>検索（空欄）→全件ポップアップ表示</t>
-  </si>
-  <si>
-    <t>空欄検索でポップアップに登録済み全7件が表示されることを確認</t>
-  </si>
-  <si>
-    <t>POS-007</t>
-  </si>
-  <si>
-    <t>検索（キーワード）→絞り込み表示</t>
-  </si>
-  <si>
-    <t>キーワード検索でポップアップに該当商品のみ表示されることを確認</t>
-  </si>
-  <si>
-    <t>POS-008</t>
-  </si>
-  <si>
-    <t>ポップアップ内検索ボックスでの再検索</t>
-  </si>
-  <si>
-    <t>ポップアップを閉じずに再検索の結果が更新されることを確認</t>
-  </si>
-  <si>
-    <t>POS-009</t>
-  </si>
-  <si>
-    <t>検索結果からカートに追加</t>
-  </si>
-  <si>
-    <t>ポップアップが閉じ、選択した商品がカートに反映されることを確認</t>
-  </si>
-  <si>
-    <t>POS-010</t>
-  </si>
-  <si>
-    <t>検索結果0件</t>
-  </si>
-  <si>
-    <t>ポップアップ内に該当なしのメッセージが表示されることを確認</t>
-  </si>
-  <si>
-    <t>POS-011</t>
-  </si>
-  <si>
-    <t>カートから商品削除</t>
-  </si>
-  <si>
-    <t>該当行がカートから削除され、合計金額が再計算されることを確認</t>
-  </si>
-  <si>
-    <t>POS-012</t>
-  </si>
-  <si>
-    <t>カートを空にする</t>
-  </si>
-  <si>
-    <t>カートが空になることを確認</t>
-  </si>
-  <si>
-    <t>POS-013</t>
-  </si>
-  <si>
-    <t>カートが空の状態での画面表示</t>
-  </si>
-  <si>
-    <t>カートが空の間は「会計へ進む」ボタンが表示されないことを確認</t>
-  </si>
-  <si>
-    <t>POS-014</t>
-  </si>
-  <si>
-    <t>会計へ進む</t>
-  </si>
-  <si>
-    <t>/pos/payment に遷移し合計金額が表示されることを確認</t>
-  </si>
-  <si>
-    <t>POS-015</t>
-  </si>
-  <si>
-    <t>お釣りのリアルタイム計算</t>
-  </si>
-  <si>
-    <t>JavaScriptにより即座にお釣り(800円)が表示されることを確認</t>
-  </si>
-  <si>
-    <t>POS-016</t>
-  </si>
-  <si>
-    <t>お預かり金額が合計未満</t>
-  </si>
-  <si>
-    <t>エラーメッセージが表示され支払い画面に留まることを確認</t>
-  </si>
-  <si>
-    <t>POS-017</t>
-  </si>
-  <si>
-    <t>会計確定（単一商品）</t>
-  </si>
-  <si>
-    <t>領収画面に遷移し合計1200円・お預かり2000円・お釣り800円が表示されることを確認</t>
-  </si>
-  <si>
-    <t>POS-018</t>
-  </si>
-  <si>
-    <t>会計確定（複数商品・複数点）</t>
-  </si>
-  <si>
-    <t>2商品(化粧水x2, 口紅x1)、合計4200円で領収画面に明細が表示されることを確認</t>
-  </si>
-  <si>
-    <t>POS-019</t>
-  </si>
-  <si>
-    <t>在庫不足での会計確定（単一商品）</t>
-  </si>
-  <si>
-    <t>在庫(10)を超える数量(11)での会計時にエラーが表示され、支払い画面に留まることを確認</t>
-  </si>
-  <si>
-    <t>POS-020</t>
-  </si>
-  <si>
-    <t>複数商品中1点だけ在庫不足（ロールバック確認）</t>
-  </si>
-  <si>
-    <t>エラーが表示され、在庫十分だった商品(C004:15)も減算されていないことを確認（トランザクションロールバック）</t>
-  </si>
-  <si>
-    <t>POS-022</t>
-  </si>
-  <si>
-    <t>お預かり金額＝合計金額ちょうど</t>
-  </si>
-  <si>
-    <t>お預かり金額が合計と同額(3500円)の場合、お釣り0円で成立することを確認</t>
-  </si>
-  <si>
-    <t>POS-021</t>
-  </si>
-  <si>
-    <t>会計後のカートクリア</t>
-  </si>
-  <si>
-    <t>会計確定後、カートが空の状態で/posに戻ることを確認</t>
-  </si>
-  <si>
-    <t>売上履歴機能 テスト結果エビデンス</t>
-  </si>
-  <si>
-    <t>全3件</t>
-  </si>
-  <si>
-    <t>SALES-002</t>
-  </si>
-  <si>
-    <t>売上0件時の表示</t>
-  </si>
-  <si>
-    <t>会計を1件も行っていない状態で空状態のメッセージが表示されることを確認</t>
+    <t>PostgreSQLはデータが永続化されるため、実データ保持のまま「売上0件」を再現するには初期化が必要。既存データ保護のため今回は未実施（結果はH2環境時点のものを維持）</t>
   </si>
   <si>
     <t>SALES-001</t>
@@ -449,7 +458,7 @@
     <t>売上履歴一覧表示</t>
   </si>
   <si>
-    <t>過去3回の会計が日時・点数・合計・お預かり・お釣りとともに一覧表示されることを確認</t>
+    <t>過去3回の会計が日時・点数・合計・お預かり・お釣りとともに一覧表示されることを確認（2026-08-26、実ブラウザ(Playwright)で再撮影）</t>
   </si>
   <si>
     <t>SALES-003</t>
@@ -473,7 +482,7 @@
     <t>初期データ投入確認</t>
   </si>
   <si>
-    <t>data.sqlの6商品(C001〜C006)がITEMテーブルに登録されていることを確認</t>
+    <t>psqlで `SELECT * FROM item;` を実行し、C001〜C006の6商品が登録されていることを確認</t>
   </si>
   <si>
     <t>DB-003</t>
@@ -482,7 +491,7 @@
     <t>テーブルスキーマ確認</t>
   </si>
   <si>
-    <t>H2コンソールのテーブルツリーに ITEM/SALE/SALE_ITEM の3テーブルが表示されていることを確認</t>
+    <t>psqlの `\dt` で item / sale / sale_item / flyway_schema_history の4テーブルが存在することを確認</t>
   </si>
   <si>
     <t>DB-004</t>
@@ -491,7 +500,7 @@
     <t>外部キー制約の確認（SALE_ITEM→SALE）</t>
   </si>
   <si>
-    <t>SALE_ITEM.SALE_ID にSALEへの外部キー制約(REFERENTIAL constraint)が存在することを確認</t>
+    <t>psqlの `\d sale_item` で "fk_sale_item_sale" FOREIGN KEY (sale_id) REFERENCES sale(id) が存在することを確認</t>
   </si>
   <si>
     <t>DB-005</t>
@@ -500,7 +509,7 @@
     <t>item_id にFK制約が無いことの確認</t>
   </si>
   <si>
-    <t>同じ結果セットに ITEM_ID を参照する外部キー制約が存在しないことを確認（スナップショット設計どおり）</t>
+    <t>psqlの `\d sale_item` の出力に item_id への外部キー制約が無いことを確認（意図的な設計どおり）</t>
   </si>
   <si>
     <t>DB-007</t>
@@ -509,7 +518,7 @@
     <t>在庫更新の即時反映確認</t>
   </si>
   <si>
-    <t>会計直後にITEM.stockが30→29へ正しく減算されていることを確認</t>
+    <t>化粧水1点会計の直後にpsqlでitem.stockが28→27に正しく減算されていることを確認</t>
   </si>
   <si>
     <t>DB-008</t>
@@ -518,7 +527,7 @@
     <t>ロールバック確認（在庫不足時）</t>
   </si>
   <si>
-    <t>SALEテーブルの件数、および商品Aの在庫がいずれも変化していないことを確認（POS-020と同一シナリオ）</t>
+    <t>ファンデーション(在庫十分)＋ネイルオイル(在庫不足)混在で会計し、エラー表示後もpsqlでsale件数・ファンデーションの在庫がいずれも変化していないことを確認（トランザクションロールバック）</t>
   </si>
   <si>
     <t>DB-006</t>
@@ -527,7 +536,7 @@
     <t>売上明細のスナップショット確認</t>
   </si>
   <si>
-    <t>商品の価格を1200円→9999円に変更した後も、過去のSALE_ITEM.unit_priceは1200円のまま保持されていることを確認</t>
+    <t>美容液の価格を3500円→9999円に変更後もpsqlで過去のsale_item.unit_priceが3500円のまま保持されていることを確認（スナップショット設計どおり）。確認後、価格・商品名は元に戻し済み</t>
   </si>
   <si>
     <t>DB-009</t>
@@ -536,16 +545,16 @@
     <t>商品コード一意制約の確認</t>
   </si>
   <si>
-    <t>H2コンソールから同じbarcode(C001)を直接INSERTすると、一意インデックス違反(Unique index or primary key violation)でエラーとなり登録が拒否されることを確認</t>
+    <t>psqlで同一barcode(C001)をINSERTすると一意制約"uk_item_barcode"違反でエラーとなり、登録が拒否されることを確認</t>
   </si>
   <si>
     <t>DB-002</t>
   </si>
   <si>
-    <t>インメモリ特性の確認（再起動でリセット）</t>
-  </si>
-  <si>
-    <t>アプリを再起動した結果、追加/変更した商品(C011追加、C001価格変更等)や売上履歴が消え、ITEMテーブルがdata.sqlの初期6件(価格も含め初期値)に戻っていることを確認</t>
+    <t>永続化の確認（再起動してもデータが保持される）</t>
+  </si>
+  <si>
+    <t>アプリ再起動前後でpsqlの item（stock含む）・sale件数を比較し、完全に一致することを確認（H2時代の「再起動でリセット」とは逆に、PostgreSQL移行によりデータが永続化されることを確認）</t>
   </si>
 </sst>
 </file>
@@ -591,7 +600,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <name val="Yu Gothic"/>
     </font>
     <font>
@@ -753,64 +762,25 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>31000</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>102499</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3619500" cy="2543175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>31000</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>102499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -837,19 +807,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -876,58 +846,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>31000</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>102500</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3619500" cy="2543175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -954,19 +885,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -993,19 +924,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1032,19 +963,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1071,19 +1002,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1110,19 +1041,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <xdr:cNvPr id="8" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1149,19 +1080,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
+        <xdr:cNvPr id="9" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1188,19 +1119,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
+        <xdr:cNvPr id="10" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1227,19 +1158,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <xdr:cNvPr id="11" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1262,6 +1193,84 @@
       <xdr:colOff>31000</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>102500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3619500" cy="2543175"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3619500" cy="2543175"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
@@ -1460,64 +1469,25 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>31000</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>102500</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3619500" cy="2543175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>31000</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>102500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1544,19 +1514,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1583,19 +1553,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1622,19 +1592,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <xdr:cNvPr id="8" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1661,19 +1631,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <xdr:cNvPr id="9" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1700,19 +1670,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
+        <xdr:cNvPr id="10" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1739,19 +1709,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
+        <xdr:cNvPr id="11" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1778,19 +1748,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <xdr:cNvPr id="12" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1817,58 +1787,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>31000</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>102500</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3619500" cy="2543175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
+        <xdr:cNvPr id="13" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1895,58 +1826,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>31000</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>102500</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3619500" cy="2543175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
+        <xdr:cNvPr id="14" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1973,19 +1865,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
+        <xdr:cNvPr id="15" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2012,19 +1904,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print"/>
+        <xdr:cNvPr id="16" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2051,19 +1943,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
+        <xdr:cNvPr id="17" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2090,19 +1982,19 @@
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print"/>
+        <xdr:cNvPr id="18" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2125,6 +2017,123 @@
       <xdr:colOff>31000</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>102500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3619500" cy="2543175"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3619500" cy="2543175"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3619500" cy="2543175"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
@@ -2206,47 +2215,47 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>31000</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>102499</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3619500" cy="2543175"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>31000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>102499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3619500" cy="2543175"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3619500" cy="2543175"/>
     <xdr:pic>
@@ -3031,24 +3040,24 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
     </row>
     <row r="9" ht="20" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -3060,16 +3069,16 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="E13" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -3078,16 +3087,16 @@
     </row>
     <row r="14" ht="40" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -3096,16 +3105,16 @@
     </row>
     <row r="15" ht="40" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>23</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -3114,16 +3123,16 @@
     </row>
     <row r="16" ht="40" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -3146,7 +3155,7 @@
     <mergeCell ref="E16:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3155,7 +3164,7 @@
   <sheetPr>
     <tabColor rgb="FFC9A961"/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B1:I19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -3167,9 +3176,10 @@
     <col min="9" max="9" width="62" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="2" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -3181,7 +3191,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3191,18 +3201,19 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="5" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>2</v>
@@ -3211,10 +3222,10 @@
         <v>4</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" ht="205" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
@@ -3222,16 +3233,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="E6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>3</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>5</v>
@@ -3252,10 +3263,10 @@
         <v>39</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>3</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>5</v>
@@ -3276,10 +3287,10 @@
         <v>42</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>3</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>5</v>
@@ -3300,10 +3311,10 @@
         <v>45</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>3</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>5</v>
@@ -3318,22 +3329,22 @@
         <v>5</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>20</v>
       </c>
       <c r="I10" s="11"/>
     </row>
@@ -3348,10 +3359,10 @@
         <v>49</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>3</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>5</v>
@@ -3366,22 +3377,22 @@
         <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>22</v>
-      </c>
       <c r="E12" s="12" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="I12" s="11"/>
     </row>
@@ -3390,22 +3401,22 @@
         <v>8</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G13" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I13" s="11"/>
     </row>
@@ -3414,22 +3425,22 @@
         <v>9</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I14" s="11"/>
     </row>
@@ -3438,22 +3449,22 @@
         <v>10</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G15" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I15" s="11"/>
     </row>
@@ -3462,22 +3473,22 @@
         <v>11</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G16" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I16" s="11"/>
     </row>
@@ -3486,22 +3497,22 @@
         <v>12</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G17" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I17" s="11"/>
     </row>
@@ -3510,22 +3521,22 @@
         <v>13</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G18" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I18" s="11"/>
     </row>
@@ -3534,22 +3545,22 @@
         <v>14</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G19" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I19" s="11"/>
     </row>
@@ -3558,7 +3569,7 @@
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
   </mergeCells>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3568,7 +3579,7 @@
   <sheetPr>
     <tabColor rgb="FFD17A9C"/>
   </sheetPr>
-  <dimension ref="B2:I27"/>
+  <dimension ref="B1:I27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -3580,9 +3591,10 @@
     <col min="9" max="9" width="62" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="2" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -3594,7 +3606,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3604,18 +3616,19 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="5" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>2</v>
@@ -3624,10 +3637,10 @@
         <v>4</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" ht="205" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
@@ -3635,22 +3648,22 @@
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6" s="11"/>
     </row>
@@ -3659,22 +3672,22 @@
         <v>2</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G7" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" s="11"/>
     </row>
@@ -3683,22 +3696,22 @@
         <v>3</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I8" s="11"/>
     </row>
@@ -3707,22 +3720,22 @@
         <v>4</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" s="11"/>
     </row>
@@ -3731,22 +3744,22 @@
         <v>5</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="I10" s="11"/>
     </row>
@@ -3755,22 +3768,22 @@
         <v>6</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G11" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I11" s="11"/>
     </row>
@@ -3779,22 +3792,22 @@
         <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G12" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I12" s="11"/>
     </row>
@@ -3803,22 +3816,22 @@
         <v>8</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G13" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I13" s="11"/>
     </row>
@@ -3827,22 +3840,22 @@
         <v>9</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I14" s="11"/>
     </row>
@@ -3851,22 +3864,22 @@
         <v>10</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G15" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I15" s="11"/>
     </row>
@@ -3875,22 +3888,22 @@
         <v>11</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E16" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G16" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I16" s="11"/>
     </row>
@@ -3899,22 +3912,22 @@
         <v>12</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G17" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I17" s="11"/>
     </row>
@@ -3923,22 +3936,22 @@
         <v>13</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G18" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I18" s="11"/>
     </row>
@@ -3947,22 +3960,22 @@
         <v>14</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G19" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I19" s="11"/>
     </row>
@@ -3971,22 +3984,22 @@
         <v>15</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G20" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I20" s="11"/>
     </row>
@@ -3995,22 +4008,22 @@
         <v>16</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E21" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I21" s="11"/>
     </row>
@@ -4019,22 +4032,22 @@
         <v>17</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I22" s="11"/>
     </row>
@@ -4043,22 +4056,22 @@
         <v>18</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G23" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I23" s="11"/>
     </row>
@@ -4067,22 +4080,22 @@
         <v>19</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E24" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I24" s="11"/>
     </row>
@@ -4091,22 +4104,22 @@
         <v>20</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E25" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G25" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I25" s="11"/>
     </row>
@@ -4115,22 +4128,22 @@
         <v>21</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E26" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G26" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I26" s="11"/>
     </row>
@@ -4139,22 +4152,22 @@
         <v>22</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E27" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G27" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I27" s="11"/>
     </row>
@@ -4163,7 +4176,7 @@
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
   </mergeCells>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4173,7 +4186,7 @@
   <sheetPr>
     <tabColor rgb="FFC9A961"/>
   </sheetPr>
-  <dimension ref="B2:I8"/>
+  <dimension ref="B1:I8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -4185,9 +4198,10 @@
     <col min="9" max="9" width="62" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="2" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4199,7 +4213,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4209,18 +4223,19 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25"/>
     <row r="5" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>2</v>
@@ -4229,10 +4244,10 @@
         <v>4</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" ht="205" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
@@ -4240,22 +4255,22 @@
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I6" s="11"/>
     </row>
@@ -4264,22 +4279,22 @@
         <v>2</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G7" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I7" s="11"/>
     </row>
@@ -4288,22 +4303,22 @@
         <v>3</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I8" s="11"/>
     </row>
@@ -4312,7 +4327,7 @@
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
   </mergeCells>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -4336,7 +4351,7 @@
   <sheetData>
     <row r="2" ht="34" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4348,7 +4363,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4360,16 +4375,16 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>2</v>
@@ -4378,10 +4393,10 @@
         <v>4</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" ht="205" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
@@ -4389,22 +4404,22 @@
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I6" s="11"/>
     </row>
@@ -4413,22 +4428,22 @@
         <v>2</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G7" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I7" s="11"/>
     </row>
@@ -4437,22 +4452,22 @@
         <v>3</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I8" s="11"/>
     </row>
@@ -4461,22 +4476,22 @@
         <v>4</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I9" s="11"/>
     </row>
@@ -4485,22 +4500,22 @@
         <v>5</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G10" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I10" s="11"/>
     </row>
@@ -4509,22 +4524,22 @@
         <v>6</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G11" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I11" s="11"/>
     </row>
@@ -4533,22 +4548,22 @@
         <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G12" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I12" s="11"/>
     </row>
@@ -4557,22 +4572,22 @@
         <v>8</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G13" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I13" s="11"/>
     </row>
@@ -4581,22 +4596,22 @@
         <v>9</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="9" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I14" s="11"/>
     </row>
@@ -4605,7 +4620,7 @@
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
   </mergeCells>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>